--- a/02_加值成品/生物/生物4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-1 神經系統與感覺　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物4-1 神經系統與感覺　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>神經系統的基本單位是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>不經大腦</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>周圍神經</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>神經元</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>脊髓</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>神經細胞</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>中樞神經包括？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>腦與脊髓</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>脊髓</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>中樞</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>連接全身的是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>周圍神經</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>脊髓</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>不經大腦</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>周圍</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>神經傳遞的是什麼訊號？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>電訊號</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>腦與脊髓</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>以電化學訊號</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>電</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>不經大腦的快速反應是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>電訊號</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>快速</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>接收刺激的構造是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>腦與脊髓</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>感受器</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>快速</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>接收</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>產生反應的構造是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>周圍神經</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>動器</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>電訊號</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>反應</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>縮手反射由什麼主導？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>脊髓</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>電訊號</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>以電化學訊號</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>腦與脊髓合稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>神經元</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>中樞神經</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>中樞</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>神經系統負責快速還緩慢傳訊？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>腦與脊髓</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>快速</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>快速</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-1 神經系統與感覺　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物4-1 神經系統與感覺　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>訊息傳遞的正確路徑？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>接收整合訊息並指揮各部反應</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>神經快速短暫,內分泌較慢持久</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>感受器傳入中樞傳出動器</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>路徑</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>反射的優點是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>反應快速保護身體</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>感受器→傳入神經→脊髓→傳出神經→肌肉,不經大腦</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>接收整合訊息並指揮各部反應</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>脊髓直接處理反應更快避免傷害</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>快速</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>大腦負責什麼功能？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>思考記憶感覺等</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>感受器→傳入神經→脊髓→傳出神經→肌肉,不經大腦</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>脊髓直接處理不必等大腦</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>高級</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>脊髓屬中樞還周圍神經？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>快速</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>神經元</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>中樞神經</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>中樞</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>膝跳反射經過大腦嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>電訊號</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>不經大腦</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>感受器</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>脊髓</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>神經元之間如何傳訊？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>快速</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>感受器</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>以電化學訊號</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>脊髓</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>傳遞</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>看到危險立刻閃避靠？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>神經系統</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>協調</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>周圍神經的作用是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>感受器傳入中樞傳出動器</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>中樞整合判斷、周圍傳達訊息</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>思考記憶感覺等</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>連接中樞與全身</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>傳達</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>眨眼閃避異物屬於？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>電訊號</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>動器</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>中樞神經</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>大腦主管思考記憶屬中樞神經嗎？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>電訊號</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>神經系統</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>中樞</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-1 神經系統與感覺　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物4-1 神經系統與感覺　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>描述縮手反射的訊息傳遞路徑？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>感受器傳入中樞傳出動器</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>感受器→傳入神經→脊髓→傳出神經→肌肉,不經大腦</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>脊髓直接處理不必等大腦</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>脊髓直接處理反應更快避免傷害</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>路徑</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何反射不經大腦反而是保護機制？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>連接中樞與全身</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>脊髓直接處理反應更快避免傷害</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>神經快速短暫,內分泌較慢持久</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>比較神經與內分泌傳訊的快慢？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>神經快速短暫,內分泌較慢持久</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>連接中樞與全身</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>反應變慢判斷力下降</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>中樞與周圍神經如何分工協調？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>脊髓直接處理反應更快避免傷害</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>脊髓直接處理不必等大腦</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>中樞整合判斷、周圍傳達訊息</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>分工</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>神經以電訊號傳遞的優勢？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>快速精準傳達訊息</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>接收整合訊息並指揮各部反應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>連接中樞與全身</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>優勢</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>若脊髓受損對反射的影響？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>相關反射可能喪失</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>連接中樞與全身</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>反應變慢判斷力下降</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>損傷</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>感受器動器在反應中的角色？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>連接中樞與全身</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>脊髓直接處理不必等大腦</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>感受器接收刺激、動器執行反應</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>神經系統如何協調全身活動？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>接收整合訊息並指揮各部反應</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>感受器傳入中樞傳出動器</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>中樞整合判斷、周圍傳達訊息</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>連接中樞與全身</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>協調</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>酒精影響神經系統可能造成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>反應變慢判斷力下降</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>感受器接收刺激、動器執行反應</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>相關反射可能喪失</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>反應快速保護身體</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>影響</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何反射能在受傷前就反應？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>脊髓直接處理不必等大腦</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>感受器傳入中樞傳出動器</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>連接中樞與全身</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>感受器接收刺激、動器執行反應</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>快速</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>神經細胞</t>
+          <t>神經細胞：神經元又稱神經細胞，是構成神經系統、負責傳遞訊息的基本單位</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>中樞</t>
+          <t>中樞：腦和脊髓合稱中樞神經，是身體處理和整合訊息的核心</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>周圍</t>
+          <t>周圍：周圍神經像網路一樣連接中樞神經和身體各部位，負責傳達訊息</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>電</t>
+          <t>電：神經細胞之間是以電訊號的方式快速傳遞訊息</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>快速</t>
+          <t>快速：反射是不經大腦思考、由脊髓直接處理的快速反應，能及時保護身體</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>接收</t>
+          <t>接收：感受器是身體接收外界刺激（如光、聲音、疼痛）的構造</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>反應</t>
+          <t>反應：動器是接收神經指令後，負責做出反應的構造，例如肌肉</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：縮手反射不經大腦，而是由脊髓直接下達指令產生反應，速度更快</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>中樞</t>
+          <t>中樞：腦和脊髓是神經系統中負責統整、下達指令的核心部分，合稱中樞神經</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>快速</t>
+          <t>快速：神經系統以電訊號傳遞訊息，速度非常快，能讓身體迅速對刺激做出反應</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>路徑</t>
+          <t>路徑：訊息由感受器接收刺激，經傳入神經送到中樞，再經傳出神經送到動器</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>快速</t>
+          <t>快速：反射不用經大腦思考，能在極短時間內做出反應保護身體避免受傷</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>高級</t>
+          <t>高級：大腦負責思考、記憶、判斷和感覺等比較複雜的高階功能</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>中樞</t>
+          <t>中樞：脊髓和腦一樣都屬於中樞神經，負責處理和傳遞訊息</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>脊髓</t>
+          <t>脊髓：膝跳反射由脊髓直接處理，不需要經過大腦思考就能完成</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>傳遞</t>
+          <t>傳遞：神經元之間是靠電化學訊號傳遞訊息，速度非常快</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>協調</t>
+          <t>協調：看到危險立刻閃避，是靠神經系統快速接收訊息並指揮身體反應</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>傳達</t>
+          <t>傳達：周圍神經負責把中樞神經的指令傳達到身體各部位，也把訊息送回中樞</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：眨眼躲避異物是一種不經過大腦思考、由脊髓或腦幹直接處理的反射動作，能快速保護眼睛</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>中樞</t>
+          <t>中樞：大腦是中樞神經系統的一部分，負責思考、記憶、判斷等高階功能</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>路徑</t>
+          <t>路徑：手碰到燙的東西，感受器接收刺激後經傳入神經到脊髓，再經傳出神經到肌肉引發縮手，全程不經大腦</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：脊髓直接處理反應不用等大腦思考，速度更快，能在受傷前及時做出保護動作</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：神經系統傳遞訊息速度快但作用時間短，內分泌系統則作用較慢但效果持久</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>分工</t>
+          <t>分工：中樞神經負責整合判斷各種訊息，周圍神經負責傳達訊息並收集回饋</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>優勢</t>
+          <t>優勢：神經以電訊號傳遞訊息，速度快又精準，能讓身體迅速做出正確反應</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>損傷</t>
+          <t>損傷：脊髓受損時，經該段脊髓處理的相關反射動作可能就無法正常進行</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>角色：感受器負責接收外界刺激，動器則負責執行身體最終做出的反應動作</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>協調</t>
+          <t>協調：神經系統接收並整合來自各處的訊息，再指揮身體各部位做出協調反應</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>影響</t>
+          <t>影響：酒精會抑制神經系統的功能，使神經傳導變慢，導致反應遲鈍、判斷力下降，這也是酒後不能開車的原因</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>快速</t>
+          <t>快速：反射動作的訊號傳到脊髓就直接下達指令，不需要先傳到大腦處理再傳回來，因此反應速度非常快，能在還沒受傷前就先做出保護動作</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-1_三種難度測驗卷.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>電訊號</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>動器</t>
+          <t>神經系統</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>脊髓</t>
+          <t>神經元</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>動器</t>
+          <t>不經大腦</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>電訊號</t>
+          <t>神經元</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>以電化學訊號</t>
+          <t>神經系統</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
